--- a/实验/研究/data/tuomin/电网建模数据_Agent整合版_V1.2/逐月分县分布式光伏.xlsx
+++ b/实验/研究/data/tuomin/电网建模数据_Agent整合版_V1.2/逐月分县分布式光伏.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21550" windowHeight="10200"/>
+    <workbookView windowWidth="19008" windowHeight="10206"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1217,22 +1217,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="5" width="14.7545454545455" customWidth="1"/>
-    <col min="6" max="6" width="13.3545454545455" customWidth="1"/>
-    <col min="7" max="7" width="13.8727272727273" customWidth="1"/>
-    <col min="8" max="13" width="12.0272727272727" customWidth="1"/>
-    <col min="14" max="15" width="9.52727272727273"/>
-    <col min="16" max="19" width="9.37272727272727"/>
-    <col min="20" max="20" width="12.8"/>
-    <col min="21" max="21" width="9.52727272727273"/>
-    <col min="22" max="24" width="9.37272727272727"/>
-    <col min="25" max="25" width="12.4363636363636" customWidth="1"/>
+    <col min="1" max="5" width="14.7543859649123" customWidth="1"/>
+    <col min="6" max="6" width="13.3508771929825" customWidth="1"/>
+    <col min="7" max="7" width="13.8684210526316" customWidth="1"/>
+    <col min="8" max="13" width="12.0263157894737" customWidth="1"/>
+    <col min="14" max="15" width="9.52631578947368"/>
+    <col min="16" max="19" width="9.36842105263158"/>
+    <col min="20" max="20" width="12.7982456140351"/>
+    <col min="21" max="21" width="9.52631578947368"/>
+    <col min="22" max="24" width="9.36842105263158"/>
+    <col min="25" max="25" width="12.4385964912281" customWidth="1"/>
     <col min="26" max="27" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:14">
+    <row r="1" ht="13.5" customHeight="1" spans="1:15">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1249,7 +1249,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>144.9346</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1380,8 +1380,12 @@
         <f t="shared" ref="N4:N11" si="0">M4-B4</f>
         <v>7.2116</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <f>SUM(B4:M4)</f>
+        <v>258.8296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1425,8 +1429,12 @@
         <f t="shared" si="0"/>
         <v>7.5477</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <f t="shared" ref="O5:O11" si="1">SUM(B5:M5)</f>
+        <v>156.8691</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -1470,8 +1478,12 @@
         <f t="shared" si="0"/>
         <v>32.6128</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>458.5758</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1515,8 +1527,12 @@
         <f t="shared" si="0"/>
         <v>26.9231</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>478.7775</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1560,8 +1576,12 @@
         <f t="shared" si="0"/>
         <v>22.3814</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>264.2795</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1605,8 +1625,12 @@
         <f t="shared" si="0"/>
         <v>22.861</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>248.2451</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1650,8 +1674,12 @@
         <f t="shared" si="0"/>
         <v>16.9768</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>281.3332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1695,8 +1723,12 @@
         <f t="shared" si="0"/>
         <v>8.4202</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O11">
+        <f t="shared" si="1"/>
+        <v>188.3845</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>23</v>
@@ -1713,7 +1745,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -1754,7 +1786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -1800,7 +1832,7 @@
         <v>233.58</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1841,7 +1873,7 @@
         <v>36.2438</v>
       </c>
       <c r="N16">
-        <f t="shared" ref="N16:N23" si="1">M16-M4</f>
+        <f t="shared" ref="N16:N23" si="2">M16-M4</f>
         <v>10.8759</v>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
         <v>33.0064</v>
       </c>
       <c r="N17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.5628</v>
       </c>
     </row>
@@ -1931,7 +1963,7 @@
         <v>112.6578</v>
       </c>
       <c r="N18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>56.1876</v>
       </c>
     </row>
@@ -1976,7 +2008,7 @@
         <v>97.638</v>
       </c>
       <c r="N19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>43.3228</v>
       </c>
     </row>
@@ -2021,7 +2053,7 @@
         <v>74.0778</v>
       </c>
       <c r="N20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>38.0682</v>
       </c>
     </row>
@@ -2066,7 +2098,7 @@
         <v>49.4494</v>
       </c>
       <c r="N21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.2144</v>
       </c>
     </row>
@@ -2111,7 +2143,7 @@
         <v>75.1448</v>
       </c>
       <c r="N22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>41.9373</v>
       </c>
     </row>
@@ -2156,7 +2188,7 @@
         <v>31.8943</v>
       </c>
       <c r="N23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.411</v>
       </c>
     </row>
@@ -2183,7 +2215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:25">
+    <row r="27" ht="16.2" spans="1:25">
       <c r="A27" s="2" t="s">
         <v>1</v>
       </c>
@@ -2250,7 +2282,7 @@
         <v>0.806331611777484</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:25">
+    <row r="28" ht="16.2" spans="1:25">
       <c r="A28" s="3" t="s">
         <v>14</v>
       </c>
@@ -2321,7 +2353,7 @@
         <v>0.718451804784397</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:25">
+    <row r="29" ht="16.2" spans="1:25">
       <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
@@ -2366,11 +2398,11 @@
         <v>12.8742</v>
       </c>
       <c r="O29" s="7">
-        <f t="shared" ref="O29:O36" si="2">F29-M16</f>
+        <f t="shared" ref="O29:O36" si="3">F29-M16</f>
         <v>9.5469</v>
       </c>
       <c r="P29" s="7">
-        <f t="shared" ref="P29:P36" si="3">M29-F29</f>
+        <f t="shared" ref="P29:P36" si="4">M29-F29</f>
         <v>3.3273</v>
       </c>
       <c r="S29" s="4" t="s">
@@ -2391,7 +2423,7 @@
         <v>1.05005658343812</v>
       </c>
     </row>
-    <row r="30" ht="16.5" spans="1:25">
+    <row r="30" ht="16.2" spans="1:25">
       <c r="A30" s="3" t="s">
         <v>16</v>
       </c>
@@ -2436,11 +2468,11 @@
         <v>13.4921</v>
       </c>
       <c r="O30" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.6374</v>
       </c>
       <c r="P30" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8547</v>
       </c>
       <c r="S30" s="4" t="s">
@@ -2461,7 +2493,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="1:25">
+    <row r="31" ht="16.2" spans="1:25">
       <c r="A31" s="3" t="s">
         <v>17</v>
       </c>
@@ -2502,26 +2534,26 @@
         <v>155.9638</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" ref="N31:N36" si="4">M31-M18</f>
+        <f t="shared" ref="N31:N36" si="5">M31-M18</f>
         <v>43.306</v>
       </c>
       <c r="O31" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17.9342</v>
       </c>
       <c r="P31" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25.3718</v>
       </c>
       <c r="S31" s="4" t="s">
         <v>34</v>
       </c>
       <c r="T31" s="5">
-        <f t="shared" ref="T31:T36" si="5">O31</f>
+        <f t="shared" ref="T31:T36" si="6">O31</f>
         <v>17.9342</v>
       </c>
       <c r="U31" s="5">
-        <f t="shared" ref="U31:U36" si="6">P31</f>
+        <f t="shared" ref="U31:U36" si="7">P31</f>
         <v>25.3718</v>
       </c>
       <c r="X31" s="9" t="s">
@@ -2531,7 +2563,7 @@
         <v>0.806331611777484</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:25">
+    <row r="32" ht="16.2" spans="1:25">
       <c r="A32" s="3" t="s">
         <v>18</v>
       </c>
@@ -2572,26 +2604,26 @@
         <v>132.5405</v>
       </c>
       <c r="N32" s="7">
+        <f t="shared" si="5"/>
+        <v>34.9025</v>
+      </c>
+      <c r="O32" s="7">
+        <f t="shared" si="3"/>
+        <v>21.1497</v>
+      </c>
+      <c r="P32" s="7">
         <f t="shared" si="4"/>
-        <v>34.9025</v>
-      </c>
-      <c r="O32" s="7">
-        <f t="shared" si="2"/>
-        <v>21.1497</v>
-      </c>
-      <c r="P32" s="7">
-        <f t="shared" si="3"/>
         <v>13.7528</v>
       </c>
       <c r="S32" s="4" t="s">
         <v>35</v>
       </c>
       <c r="T32" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>21.1497</v>
       </c>
       <c r="U32" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.7528</v>
       </c>
       <c r="X32" s="9" t="s">
@@ -2601,7 +2633,7 @@
         <v>0.718451804784397</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="1:25">
+    <row r="33" ht="16.2" spans="1:25">
       <c r="A33" s="3" t="s">
         <v>19</v>
       </c>
@@ -2642,26 +2674,26 @@
         <v>99.3979</v>
       </c>
       <c r="N33" s="7">
+        <f t="shared" si="5"/>
+        <v>25.3201</v>
+      </c>
+      <c r="O33" s="7">
+        <f t="shared" si="3"/>
+        <v>18.6036</v>
+      </c>
+      <c r="P33" s="7">
         <f t="shared" si="4"/>
-        <v>25.3201</v>
-      </c>
-      <c r="O33" s="7">
-        <f t="shared" si="2"/>
-        <v>18.6036</v>
-      </c>
-      <c r="P33" s="7">
-        <f t="shared" si="3"/>
         <v>6.71650000000001</v>
       </c>
       <c r="S33" s="4" t="s">
         <v>36</v>
       </c>
       <c r="T33" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>18.6036</v>
       </c>
       <c r="U33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.71650000000001</v>
       </c>
       <c r="X33" s="9" t="s">
@@ -2671,7 +2703,7 @@
         <v>1.05005658343812</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="1:25">
+    <row r="34" ht="16.2" spans="1:25">
       <c r="A34" s="3" t="s">
         <v>20</v>
       </c>
@@ -2712,30 +2744,30 @@
         <v>59.2812</v>
       </c>
       <c r="N34" s="7">
+        <f t="shared" si="5"/>
+        <v>9.8318</v>
+      </c>
+      <c r="O34" s="7">
+        <f t="shared" si="3"/>
+        <v>6.3351</v>
+      </c>
+      <c r="P34" s="7">
         <f t="shared" si="4"/>
-        <v>9.8318</v>
-      </c>
-      <c r="O34" s="7">
-        <f t="shared" si="2"/>
-        <v>6.3351</v>
-      </c>
-      <c r="P34" s="7">
-        <f t="shared" si="3"/>
         <v>3.4967</v>
       </c>
       <c r="S34" s="4" t="s">
         <v>37</v>
       </c>
       <c r="T34" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.3351</v>
       </c>
       <c r="U34" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.4967</v>
       </c>
     </row>
-    <row r="35" ht="16.5" spans="1:25">
+    <row r="35" ht="16.2" spans="1:25">
       <c r="A35" s="3" t="s">
         <v>21</v>
       </c>
@@ -2776,11 +2808,11 @@
         <v>103.1678</v>
       </c>
       <c r="N35" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>28.023</v>
       </c>
       <c r="O35" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>34.3636</v>
       </c>
       <c r="P35" s="7">
@@ -2791,15 +2823,15 @@
         <v>38</v>
       </c>
       <c r="T35" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>34.3636</v>
       </c>
       <c r="U35" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.65940000000001</v>
       </c>
     </row>
-    <row r="36" ht="16.5" spans="1:25">
+    <row r="36" ht="16.2" spans="1:25">
       <c r="A36" s="3" t="s">
         <v>22</v>
       </c>
@@ -2840,26 +2872,26 @@
         <v>63.3798</v>
       </c>
       <c r="N36" s="7">
+        <f t="shared" si="5"/>
+        <v>31.4855</v>
+      </c>
+      <c r="O36" s="7">
+        <f t="shared" si="3"/>
+        <v>13.0877</v>
+      </c>
+      <c r="P36" s="7">
         <f t="shared" si="4"/>
-        <v>31.4855</v>
-      </c>
-      <c r="O36" s="7">
-        <f t="shared" si="2"/>
-        <v>13.0877</v>
-      </c>
-      <c r="P36" s="7">
-        <f t="shared" si="3"/>
         <v>18.3978</v>
       </c>
       <c r="S36" s="4" t="s">
         <v>39</v>
       </c>
       <c r="T36" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13.0877</v>
       </c>
       <c r="U36" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>18.3978</v>
       </c>
     </row>
@@ -2908,27 +2940,27 @@
         <v>14</v>
       </c>
       <c r="B41" s="13">
-        <f t="shared" ref="B41:G41" si="7">SUM(B42:B49)</f>
+        <f t="shared" ref="B41:G41" si="8">SUM(B42:B49)</f>
         <v>727.9129</v>
       </c>
       <c r="C41" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>741.401</v>
       </c>
       <c r="D41" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>750.3566</v>
       </c>
       <c r="E41" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>760.44910075</v>
       </c>
       <c r="F41" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>774.1931</v>
       </c>
       <c r="G41" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>787.406</v>
       </c>
       <c r="H41">
@@ -2963,7 +2995,7 @@
         <v>57.2288</v>
       </c>
       <c r="H42">
-        <f t="shared" ref="H42:H49" si="8">G42-M29</f>
+        <f t="shared" ref="H42:H49" si="9">G42-M29</f>
         <v>8.1108</v>
       </c>
       <c r="K42" s="14">
@@ -2993,7 +3025,7 @@
         <v>52.7764</v>
       </c>
       <c r="H43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.2779</v>
       </c>
       <c r="J43">
@@ -3027,7 +3059,7 @@
         <v>180.0876</v>
       </c>
       <c r="H44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>24.1238</v>
       </c>
       <c r="K44" s="14">
@@ -3057,7 +3089,7 @@
         <v>148.7795</v>
       </c>
       <c r="H45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>16.239</v>
       </c>
     </row>
@@ -3084,7 +3116,7 @@
         <v>109.7064</v>
       </c>
       <c r="H46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.3085</v>
       </c>
     </row>
@@ -3111,7 +3143,7 @@
         <v>61.5908</v>
       </c>
       <c r="H47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.3096</v>
       </c>
     </row>
@@ -3138,7 +3170,7 @@
         <v>108.3176</v>
       </c>
       <c r="H48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.1498</v>
       </c>
     </row>
@@ -3165,7 +3197,7 @@
         <v>68.9189</v>
       </c>
       <c r="H49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.53909999999999</v>
       </c>
     </row>
@@ -3186,7 +3218,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3198,7 +3230,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
